--- a/AAII_Financials/Yearly/LMT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LMT_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>LMT</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>67571000</v>
+      </c>
+      <c r="E8" s="3">
         <v>65984000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>67044000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>65398000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>59812000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>53762000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>49960000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>47290000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>40536000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>39946000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>45358000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>47182000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>46499000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>59000000</v>
+      </c>
+      <c r="E9" s="3">
         <v>57597000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>57947000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>56717000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>51445000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>46325000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>43739000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>41875000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>35764000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>35196000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>40775000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>42938000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>119519000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8571000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8387000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9097000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8681000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8367000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7437000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6221000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5415000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4772000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4750000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4583000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4244000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-73020000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,51 +961,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1634000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1736000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>27000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-34000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>96000</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>80000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>82000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>119000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>396000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>48000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>136000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>59064000</v>
+      </c>
+      <c r="E17" s="3">
         <v>59170000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>59621000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>56754000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>51267000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>46428000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>43216000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41402000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35824000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>34934000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>40853000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>42748000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>42479000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8507000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6814000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7423000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8644000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8545000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7334000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6744000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5888000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4712000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5012000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4505000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4434000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4020000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>507000</v>
+      </c>
+      <c r="E20" s="3">
         <v>489000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>696000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>182000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-651000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-828000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-847000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-471000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>30000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5000</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>21000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-35000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10444000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8707000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>9483000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>10116000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9083000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7667000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7092000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6632000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5768000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6011000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5495000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5443000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4993000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>916000</v>
+      </c>
+      <c r="E22" s="3">
         <v>623000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>569000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>591000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>653000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>668000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>651000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>663000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>443000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>340000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>350000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>383000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>354000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8098000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6680000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7550000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8235000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7241000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5838000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5246000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4754000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4299000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4677000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4155000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4072000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3631000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1178000</v>
+      </c>
+      <c r="E24" s="3">
         <v>948000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1235000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1347000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1011000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>835000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1470000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1093000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1173000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1424000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1205000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1327000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>964000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6920000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5732000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6315000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6888000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6230000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5003000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3776000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3661000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3126000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3253000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2950000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2745000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2667000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6920000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5732000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6315000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6888000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6230000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5003000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3776000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3661000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3126000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3253000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2950000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2745000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2655000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,51 +1581,57 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-55000</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>43000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-1813000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>1512000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>479000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>361000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>31000</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-12000</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-507000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-489000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-696000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-182000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>651000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>828000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>847000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>471000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-30000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5000</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-21000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>35000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6920000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5732000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6315000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6833000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6230000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5046000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1963000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5173000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3605000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3614000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2981000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2745000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2643000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6920000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5732000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6315000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6833000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6230000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5046000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1963000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5173000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3605000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3614000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2981000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2745000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2643000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,50 +1987,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1442000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2547000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3604000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3160000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1514000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>772000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2861000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1837000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1090000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1446000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2617000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1898000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3582000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1983,305 +2072,329 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>3000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15315000</v>
+      </c>
+      <c r="E43" s="3">
         <v>14823000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12542000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11523000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11431000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11916000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10257000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8202000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7254000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5877000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5834000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6563000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6064000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3132000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3088000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2981000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3545000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3619000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2997000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9388000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4670000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4819000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2804000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2977000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2937000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4962000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>632000</v>
+      </c>
+      <c r="E45" s="3">
         <v>533000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>688000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1150000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>531000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>418000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1509000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>399000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2873000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2195000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1901000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2457000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1967000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20521000</v>
+      </c>
+      <c r="E46" s="3">
         <v>20991000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19815000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19378000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17095000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16103000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17505000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15108000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14573000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12322000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13329000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13855000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14094000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2501000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2285000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2789000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>1200000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>1400000</v>
       </c>
       <c r="J47" s="3">
         <v>1400000</v>
       </c>
       <c r="K47" s="3">
+        <v>1400000</v>
+      </c>
+      <c r="L47" s="3">
         <v>1300000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>971000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>914000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>749000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1394000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9470000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9075000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8897000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7213000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7591000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6124000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11550000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5549000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10879000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4751000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4706000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4675000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9222000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14411000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14158000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14296000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13818000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13817000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14263000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18401000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14857000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18864000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11186000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10348000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10370000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11012000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5553000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6371000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5076000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10301000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9025000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7186000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12906000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10892000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18572000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7816000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6891000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9008000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11464000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>52456000</v>
+      </c>
+      <c r="E54" s="3">
         <v>52880000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>50873000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>50710000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>47528000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44876000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>46620000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>47806000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>49304000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37046000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36188000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>38657000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>37908000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,260 +2655,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2312000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2117000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>780000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>880000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1281000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2402000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1467000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1653000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1745000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1562000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1397000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2038000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2269000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>500000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1250000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1500000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>750000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>956000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>150000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14457000</v>
+      </c>
+      <c r="E59" s="3">
         <v>13770000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13211000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12553000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11441000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10496000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17448000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10889000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11217000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9550000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9723000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9967000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9861000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16937000</v>
+      </c>
+      <c r="E60" s="3">
         <v>15887000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13997000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13933000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13972000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14398000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12913000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12542000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13918000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11112000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11120000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12155000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12130000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17291000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15429000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11670000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11669000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11404000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12604000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13513000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14282000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14305000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6142000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6152000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6158000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6460000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11393000</v>
+      </c>
+      <c r="E62" s="3">
         <v>12298000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14247000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>19070000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18981000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>16425000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>20970000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>19376000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17779000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16392000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13998000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20305000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18317000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45621000</v>
+      </c>
+      <c r="E66" s="3">
         <v>43614000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>39914000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>44695000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>44401000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>43482000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47470000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>46295000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>46207000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>33646000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31270000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38618000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>36907000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15398000</v>
+      </c>
+      <c r="E72" s="3">
         <v>16943000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21600000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>21636000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18401000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15434000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11405000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13324000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14238000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14956000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14200000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13211000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11937000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6835000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9266000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10959000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6015000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3127000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1394000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-850000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1511000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3097000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3400000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4918000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>39000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1001000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6920000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5732000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6315000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6833000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6230000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5046000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1963000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5173000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3605000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3614000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2981000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2745000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2643000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1430000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1404000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1364000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1290000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1189000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1161000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1195000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1215000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1026000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>994000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>990000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>988000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1008000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7920000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7802000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9221000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8183000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7311000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3138000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6476000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5189000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5101000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3866000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4546000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1561000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4253000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1691000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1670000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1522000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1766000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1484000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1278000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1177000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1063000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-939000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-845000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-836000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-942000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1160000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1694000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1789000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1161000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2010000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1241000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1075000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1147000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-985000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9734000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1723000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1121000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1177000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-788000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,50 +4221,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3056000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3016000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2940000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2764000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-2556000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-2347000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-2163000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2048000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1932000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1760000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1540000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1352000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1095000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,51 +4398,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7331000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7070000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7616000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4527000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5328000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4152000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4305000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3457000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4277000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3314000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2706000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2068000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2144000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4240,49 +4488,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1105000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1057000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>444000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1646000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>742000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2089000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1024000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>747000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-356000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1171000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>719000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1684000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1321000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LMT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LMT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>LMT</t>
   </si>
@@ -787,10 +787,10 @@
         <v>51445000</v>
       </c>
       <c r="I9" s="3">
-        <v>46325000</v>
+        <v>46392000</v>
       </c>
       <c r="J9" s="3">
-        <v>43739000</v>
+        <v>43589000</v>
       </c>
       <c r="K9" s="3">
         <v>41875000</v>
@@ -832,10 +832,10 @@
         <v>8367000</v>
       </c>
       <c r="I10" s="3">
-        <v>7437000</v>
+        <v>7370000</v>
       </c>
       <c r="J10" s="3">
-        <v>6221000</v>
+        <v>6371000</v>
       </c>
       <c r="K10" s="3">
         <v>5415000</v>
@@ -880,26 +880,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>1500000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1700000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1500000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1200000</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>92000</v>
+        <v>156000</v>
       </c>
       <c r="E14" s="3">
-        <v>1634000</v>
+        <v>214000</v>
       </c>
       <c r="F14" s="3">
-        <v>1736000</v>
+        <v>-229000</v>
       </c>
       <c r="G14" s="3">
-        <v>27000</v>
+        <v>155000</v>
       </c>
       <c r="H14" s="3">
-        <v>-34000</v>
+        <v>-85000</v>
       </c>
       <c r="I14" s="3">
-        <v>96000</v>
+        <v>206000</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-134000</v>
       </c>
       <c r="K14" s="3">
         <v>80000</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1167000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1151000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1189000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1124000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1078000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1055000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1072000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>59064000</v>
+        <v>58513000</v>
       </c>
       <c r="E17" s="3">
-        <v>59170000</v>
+        <v>58515000</v>
       </c>
       <c r="F17" s="3">
-        <v>59621000</v>
+        <v>59223000</v>
       </c>
       <c r="G17" s="3">
-        <v>56754000</v>
+        <v>56521000</v>
       </c>
       <c r="H17" s="3">
-        <v>51267000</v>
+        <v>52114000</v>
       </c>
       <c r="I17" s="3">
-        <v>46428000</v>
+        <v>47118000</v>
       </c>
       <c r="J17" s="3">
-        <v>43216000</v>
+        <v>44367000</v>
       </c>
       <c r="K17" s="3">
         <v>41402000</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8507000</v>
+        <v>9058000</v>
       </c>
       <c r="E18" s="3">
-        <v>6814000</v>
+        <v>7469000</v>
       </c>
       <c r="F18" s="3">
-        <v>7423000</v>
+        <v>7821000</v>
       </c>
       <c r="G18" s="3">
-        <v>8644000</v>
+        <v>8877000</v>
       </c>
       <c r="H18" s="3">
-        <v>8545000</v>
+        <v>7698000</v>
       </c>
       <c r="I18" s="3">
-        <v>7334000</v>
+        <v>6644000</v>
       </c>
       <c r="J18" s="3">
-        <v>6744000</v>
+        <v>5593000</v>
       </c>
       <c r="K18" s="3">
         <v>5888000</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>507000</v>
+        <v>-112000</v>
       </c>
       <c r="E20" s="3">
-        <v>489000</v>
+        <v>-48000</v>
       </c>
       <c r="F20" s="3">
-        <v>696000</v>
+        <v>-69000</v>
       </c>
       <c r="G20" s="3">
-        <v>182000</v>
+        <v>-104000</v>
       </c>
       <c r="H20" s="3">
-        <v>-651000</v>
+        <v>-111000</v>
       </c>
       <c r="I20" s="3">
-        <v>-828000</v>
+        <v>-68000</v>
       </c>
       <c r="J20" s="3">
-        <v>-847000</v>
+        <v>-170000</v>
       </c>
       <c r="K20" s="3">
         <v>-471000</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>10444000</v>
+        <v>10337000</v>
       </c>
       <c r="E21" s="3">
-        <v>8707000</v>
+        <v>8668000</v>
       </c>
       <c r="F21" s="3">
-        <v>9483000</v>
+        <v>9079000</v>
       </c>
       <c r="G21" s="3">
-        <v>10116000</v>
+        <v>10105000</v>
       </c>
       <c r="H21" s="3">
-        <v>9083000</v>
+        <v>8887000</v>
       </c>
       <c r="I21" s="3">
-        <v>7667000</v>
+        <v>7767000</v>
       </c>
       <c r="J21" s="3">
-        <v>7092000</v>
+        <v>6835000</v>
       </c>
       <c r="K21" s="3">
         <v>6632000</v>
@@ -1381,10 +1381,10 @@
         <v>1011000</v>
       </c>
       <c r="I24" s="3">
-        <v>835000</v>
+        <v>792000</v>
       </c>
       <c r="J24" s="3">
-        <v>1470000</v>
+        <v>3356000</v>
       </c>
       <c r="K24" s="3">
         <v>1093000</v>
@@ -1471,10 +1471,10 @@
         <v>6230000</v>
       </c>
       <c r="I26" s="3">
-        <v>5003000</v>
+        <v>5046000</v>
       </c>
       <c r="J26" s="3">
-        <v>3776000</v>
+        <v>1890000</v>
       </c>
       <c r="K26" s="3">
         <v>3661000</v>
@@ -1510,16 +1510,16 @@
         <v>6315000</v>
       </c>
       <c r="G27" s="3">
-        <v>6888000</v>
+        <v>6833000</v>
       </c>
       <c r="H27" s="3">
         <v>6230000</v>
       </c>
       <c r="I27" s="3">
-        <v>5003000</v>
+        <v>5046000</v>
       </c>
       <c r="J27" s="3">
-        <v>3776000</v>
+        <v>1963000</v>
       </c>
       <c r="K27" s="3">
         <v>3661000</v>
@@ -1590,11 +1590,11 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1606,10 +1606,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>43000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-1813000</v>
+        <v>73000</v>
       </c>
       <c r="K29" s="3">
         <v>1512000</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-507000</v>
+        <v>112000</v>
       </c>
       <c r="E32" s="3">
-        <v>-489000</v>
+        <v>48000</v>
       </c>
       <c r="F32" s="3">
-        <v>-696000</v>
+        <v>69000</v>
       </c>
       <c r="G32" s="3">
-        <v>-182000</v>
+        <v>104000</v>
       </c>
       <c r="H32" s="3">
-        <v>651000</v>
+        <v>111000</v>
       </c>
       <c r="I32" s="3">
-        <v>828000</v>
+        <v>68000</v>
       </c>
       <c r="J32" s="3">
-        <v>847000</v>
+        <v>170000</v>
       </c>
       <c r="K32" s="3">
         <v>471000</v>
@@ -2147,7 +2147,7 @@
         <v>2997000</v>
       </c>
       <c r="J44" s="3">
-        <v>9388000</v>
+        <v>2878000</v>
       </c>
       <c r="K44" s="3">
         <v>4670000</v>
@@ -2264,19 +2264,19 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2501000</v>
+        <v>701000</v>
       </c>
       <c r="E47" s="3">
-        <v>2285000</v>
+        <v>685000</v>
       </c>
       <c r="F47" s="3">
-        <v>2789000</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
+        <v>689000</v>
+      </c>
+      <c r="G47" s="3">
+        <v>784000</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1200000</v>
       </c>
       <c r="I47" s="3">
         <v>1200000</v>
@@ -2312,22 +2312,22 @@
         <v>9470000</v>
       </c>
       <c r="E48" s="3">
-        <v>9075000</v>
+        <v>7975000</v>
       </c>
       <c r="F48" s="3">
-        <v>8897000</v>
+        <v>7597000</v>
       </c>
       <c r="G48" s="3">
         <v>7213000</v>
       </c>
       <c r="H48" s="3">
-        <v>7591000</v>
+        <v>6591000</v>
       </c>
       <c r="I48" s="3">
         <v>6124000</v>
       </c>
       <c r="J48" s="3">
-        <v>11550000</v>
+        <v>5775000</v>
       </c>
       <c r="K48" s="3">
         <v>5549000</v>
@@ -2363,16 +2363,16 @@
         <v>14296000</v>
       </c>
       <c r="G49" s="3">
-        <v>13818000</v>
+        <v>14504000</v>
       </c>
       <c r="H49" s="3">
-        <v>13817000</v>
+        <v>14328000</v>
       </c>
       <c r="I49" s="3">
-        <v>14263000</v>
+        <v>14710000</v>
       </c>
       <c r="J49" s="3">
-        <v>18401000</v>
+        <v>15028000</v>
       </c>
       <c r="K49" s="3">
         <v>14857000</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5553000</v>
+        <v>4400000</v>
       </c>
       <c r="E52" s="3">
-        <v>6371000</v>
+        <v>5327000</v>
       </c>
       <c r="F52" s="3">
-        <v>5076000</v>
+        <v>6186000</v>
       </c>
       <c r="G52" s="3">
-        <v>10301000</v>
+        <v>5356000</v>
       </c>
       <c r="H52" s="3">
-        <v>9025000</v>
+        <v>4995000</v>
       </c>
       <c r="I52" s="3">
-        <v>7186000</v>
+        <v>3531000</v>
       </c>
       <c r="J52" s="3">
-        <v>12906000</v>
+        <v>3756000</v>
       </c>
       <c r="K52" s="3">
         <v>10892000</v>
@@ -2707,13 +2707,13 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>168000</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
+        <v>483000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>118000</v>
       </c>
       <c r="F58" s="3">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>500000</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>14457000</v>
+        <v>11009000</v>
       </c>
       <c r="E59" s="3">
-        <v>13770000</v>
+        <v>10577000</v>
       </c>
       <c r="F59" s="3">
-        <v>13211000</v>
+        <v>10109000</v>
       </c>
       <c r="G59" s="3">
-        <v>12553000</v>
+        <v>9390000</v>
       </c>
       <c r="H59" s="3">
-        <v>11441000</v>
+        <v>8975000</v>
       </c>
       <c r="I59" s="3">
-        <v>10496000</v>
+        <v>8374000</v>
       </c>
       <c r="J59" s="3">
-        <v>17448000</v>
+        <v>8911000</v>
       </c>
       <c r="K59" s="3">
         <v>10889000</v>
@@ -2842,7 +2842,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>17291000</v>
+        <v>18153000</v>
       </c>
       <c r="E61" s="3">
         <v>15429000</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11393000</v>
+        <v>4369000</v>
       </c>
       <c r="E62" s="3">
-        <v>12298000</v>
+        <v>6826000</v>
       </c>
       <c r="F62" s="3">
-        <v>14247000</v>
+        <v>5928000</v>
       </c>
       <c r="G62" s="3">
-        <v>19070000</v>
+        <v>6196000</v>
       </c>
       <c r="H62" s="3">
-        <v>18981000</v>
+        <v>5747000</v>
       </c>
       <c r="I62" s="3">
-        <v>16425000</v>
+        <v>4311000</v>
       </c>
       <c r="J62" s="3">
-        <v>20970000</v>
+        <v>4548000</v>
       </c>
       <c r="K62" s="3">
         <v>19376000</v>
@@ -3076,16 +3076,16 @@
         <v>39914000</v>
       </c>
       <c r="G66" s="3">
-        <v>44695000</v>
+        <v>44672000</v>
       </c>
       <c r="H66" s="3">
-        <v>44401000</v>
+        <v>44357000</v>
       </c>
       <c r="I66" s="3">
-        <v>43482000</v>
+        <v>43427000</v>
       </c>
       <c r="J66" s="3">
-        <v>47470000</v>
+        <v>47396000</v>
       </c>
       <c r="K66" s="3">
         <v>46295000</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1430000</v>
+        <v>920000</v>
       </c>
       <c r="E83" s="3">
-        <v>1404000</v>
+        <v>903000</v>
       </c>
       <c r="F83" s="3">
-        <v>1364000</v>
+        <v>904000</v>
       </c>
       <c r="G83" s="3">
-        <v>1290000</v>
+        <v>853000</v>
       </c>
       <c r="H83" s="3">
-        <v>1189000</v>
+        <v>794000</v>
       </c>
       <c r="I83" s="3">
-        <v>1161000</v>
+        <v>759000</v>
       </c>
       <c r="J83" s="3">
-        <v>1195000</v>
+        <v>760000</v>
       </c>
       <c r="K83" s="3">
         <v>1215000</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3056000</v>
+        <v>3056000</v>
       </c>
       <c r="E96" s="3">
-        <v>-3016000</v>
+        <v>3016000</v>
       </c>
       <c r="F96" s="3">
-        <v>-2940000</v>
+        <v>2940000</v>
       </c>
       <c r="G96" s="3">
-        <v>-2764000</v>
+        <v>2764000</v>
       </c>
       <c r="H96" s="3">
-        <v>-2556000</v>
+        <v>2556000</v>
       </c>
       <c r="I96" s="3">
-        <v>-2347000</v>
+        <v>2347000</v>
       </c>
       <c r="J96" s="3">
-        <v>-2163000</v>
+        <v>2163000</v>
       </c>
       <c r="K96" s="3">
         <v>-2048000</v>
@@ -4452,26 +4452,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/LMT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LMT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>LMT</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>71043000</v>
+      </c>
+      <c r="E8" s="3">
         <v>67571000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>65984000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>67044000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>65398000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>59812000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>53762000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>49960000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>47290000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>40536000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>39946000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>45358000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>47182000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>46499000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>64026000</v>
+      </c>
+      <c r="E9" s="3">
         <v>59000000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>57597000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>57947000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>56717000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>51445000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>46392000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>43589000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>41875000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>35764000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>35196000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>40775000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>42938000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>119519000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7017000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8571000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8387000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9097000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8681000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8367000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7370000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6371000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5415000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4772000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4750000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4583000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4244000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-73020000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,22 +887,23 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1600000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1500000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1700000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1500000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1300000</v>
       </c>
       <c r="H12" s="3">
         <v>1300000</v>
@@ -899,10 +912,10 @@
         <v>1300000</v>
       </c>
       <c r="J12" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="K12" s="3">
         <v>1200000</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,81 +980,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E14" s="3">
         <v>156000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>214000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-229000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>155000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-85000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>206000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-134000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>80000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>82000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>119000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>396000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>48000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>136000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1213000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1167000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1151000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1189000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1124000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1078000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1055000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1072000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>63862000</v>
+      </c>
+      <c r="E17" s="3">
         <v>58513000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>58515000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>59223000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>56521000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>52114000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>47118000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>44367000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>41402000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>35824000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34934000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>40853000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>42748000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>42479000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7181000</v>
+      </c>
+      <c r="E18" s="3">
         <v>9058000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7469000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7821000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8877000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7698000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6644000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5593000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5888000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4712000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5012000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4505000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4434000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4020000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,233 +1212,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-140000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-112000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-48000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-69000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-104000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-111000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-68000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-170000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-471000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>30000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5000</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>21000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-35000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8534000</v>
+      </c>
+      <c r="E21" s="3">
         <v>10337000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8668000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9079000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10105000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8887000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7767000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6835000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6632000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5768000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6011000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5495000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5443000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4993000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1036000</v>
+      </c>
+      <c r="E22" s="3">
         <v>916000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>623000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>569000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>591000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>653000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>668000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>651000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>663000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>443000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>340000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>350000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>383000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>354000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6220000</v>
+      </c>
+      <c r="E23" s="3">
         <v>8098000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6680000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7550000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8235000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7241000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5838000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5246000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4754000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4299000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4677000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4155000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4072000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3631000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>884000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1178000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>948000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1235000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1347000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1011000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>792000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3356000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1093000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1173000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1424000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1205000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1327000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>964000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5336000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6920000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5732000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6315000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6888000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6230000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5046000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1890000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3661000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3126000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3253000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2950000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2745000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2667000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5336000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6920000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5732000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6315000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6833000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6230000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5046000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1963000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3661000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3126000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3253000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2950000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2745000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2655000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1600,38 +1660,41 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-55000</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>73000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>1512000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>479000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>361000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>31000</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E32" s="3">
         <v>112000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>48000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>69000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>104000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>111000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>68000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>170000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>471000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-30000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5000</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-21000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>35000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5336000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6920000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5732000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6315000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6833000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6230000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5046000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1963000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5173000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3605000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3614000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2981000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2745000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2643000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5336000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6920000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5732000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6315000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6833000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6230000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5046000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1963000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5173000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3605000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3614000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2981000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2745000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2643000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,53 +2073,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2483000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1442000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2547000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3604000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3160000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1514000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>772000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2861000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1837000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1090000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1446000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2617000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1898000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3582000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2075,326 +2164,350 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>3000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15308000</v>
+      </c>
+      <c r="E43" s="3">
         <v>15315000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14823000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12542000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11523000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11431000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11916000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10257000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8202000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7254000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5877000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5834000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6563000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6064000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3474000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3132000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3088000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2981000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3545000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3619000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2997000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2878000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4670000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4819000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2804000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2977000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2937000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4962000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>584000</v>
+      </c>
+      <c r="E45" s="3">
         <v>632000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>533000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>688000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1150000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>531000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>418000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1509000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>399000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2873000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2195000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1901000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2457000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1967000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21849000</v>
+      </c>
+      <c r="E46" s="3">
         <v>20521000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20991000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19815000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19378000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17095000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16103000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17505000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15108000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14573000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12322000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13329000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13855000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14094000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>654000</v>
+      </c>
+      <c r="E47" s="3">
         <v>701000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>685000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>689000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>784000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1200000</v>
       </c>
       <c r="I47" s="3">
         <v>1200000</v>
       </c>
       <c r="J47" s="3">
-        <v>1400000</v>
+        <v>1200000</v>
       </c>
       <c r="K47" s="3">
         <v>1400000</v>
       </c>
       <c r="L47" s="3">
+        <v>1400000</v>
+      </c>
+      <c r="M47" s="3">
         <v>1300000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>971000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>914000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>749000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1394000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9470000</v>
+        <v>9726000</v>
       </c>
       <c r="E48" s="3">
+        <v>8370000</v>
+      </c>
+      <c r="F48" s="3">
         <v>7975000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7597000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7213000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6591000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6124000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5775000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5549000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10879000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4751000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4706000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4675000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9222000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14982000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14411000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14158000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14296000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14504000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14328000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14710000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15028000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14857000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18864000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11186000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10348000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10370000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11012000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4400000</v>
+        <v>4849000</v>
       </c>
       <c r="E52" s="3">
+        <v>5500000</v>
+      </c>
+      <c r="F52" s="3">
         <v>5327000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6186000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5356000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4995000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3531000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3756000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10892000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18572000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7816000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6891000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9008000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11464000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>55617000</v>
+      </c>
+      <c r="E54" s="3">
         <v>52456000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>52880000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>50873000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>50710000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>47528000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44876000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>46620000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>47806000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>49304000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>37046000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36188000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>38657000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37908000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,278 +2785,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2222000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2312000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2117000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>780000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>880000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1281000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2402000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1467000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1653000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1745000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1562000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1397000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2038000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2269000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>483000</v>
+        <v>958000</v>
       </c>
       <c r="E58" s="3">
+        <v>168000</v>
+      </c>
+      <c r="F58" s="3">
         <v>118000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>500000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1250000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1500000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>750000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>956000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>150000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>11009000</v>
+        <v>13115000</v>
       </c>
       <c r="E59" s="3">
+        <v>11324000</v>
+      </c>
+      <c r="F59" s="3">
         <v>10577000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10109000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9390000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8975000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8374000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8911000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10889000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11217000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9550000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9723000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9967000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9861000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19420000</v>
+      </c>
+      <c r="E60" s="3">
         <v>16937000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15887000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13997000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13933000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13972000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14398000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12913000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12542000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13918000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11112000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11120000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12155000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12130000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18153000</v>
+        <v>20460000</v>
       </c>
       <c r="E61" s="3">
+        <v>17291000</v>
+      </c>
+      <c r="F61" s="3">
         <v>15429000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11670000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11669000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11404000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12604000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13513000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14282000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14305000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6142000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6152000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6158000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6460000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4369000</v>
+        <v>4613000</v>
       </c>
       <c r="E62" s="3">
+        <v>5231000</v>
+      </c>
+      <c r="F62" s="3">
         <v>6826000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5928000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6196000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5747000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4311000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4548000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19376000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>17779000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16392000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13998000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20305000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18317000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>49284000</v>
+      </c>
+      <c r="E66" s="3">
         <v>45621000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>43614000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39914000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>44672000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>44357000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>43427000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47396000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>46295000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>46207000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33646000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>31270000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>38618000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>36907000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14551000</v>
+      </c>
+      <c r="E72" s="3">
         <v>15398000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16943000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>21600000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21636000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18401000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15434000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11405000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13324000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14238000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14956000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14200000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13211000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11937000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6333000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6835000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9266000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10959000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6015000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3127000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1394000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-850000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1511000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3097000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3400000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4918000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>39000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1001000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5336000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6920000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5732000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6315000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6833000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6230000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5046000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1963000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5173000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3605000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3614000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2981000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2745000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2643000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>966000</v>
+      </c>
+      <c r="E83" s="3">
         <v>920000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>903000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>904000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>853000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>794000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>759000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>760000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1215000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1026000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>994000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>990000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>988000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1008000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6972000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7920000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7802000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9221000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8183000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7311000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3138000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6476000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5189000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5101000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3866000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4546000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1561000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4253000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1685000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1691000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1670000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1522000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1766000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1484000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1278000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1177000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1063000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-939000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-845000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-836000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-942000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1160000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1792000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1694000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1789000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1161000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2010000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1241000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1075000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1147000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-985000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9734000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1723000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1121000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1177000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-788000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,53 +4454,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3059000</v>
+      </c>
+      <c r="E96" s="3">
         <v>3056000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3016000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2940000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2764000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2556000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2347000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2163000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2048000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1932000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1760000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1540000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1352000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1095000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,54 +4643,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4139000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7331000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7070000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7616000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4527000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5328000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4152000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4305000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3457000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4277000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3314000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2706000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2068000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2144000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4473,8 +4721,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4491,52 +4739,58 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1041000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1105000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1057000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>444000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1646000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>742000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2089000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1024000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>747000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-356000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1171000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>719000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1684000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1321000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LMT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LMT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>LMT</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>75048000</v>
+      </c>
+      <c r="E8" s="3">
         <v>71043000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>67571000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>65984000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>67044000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>65398000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>59812000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>53762000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>49960000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>47290000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>40536000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>39946000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>45358000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>47182000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>46499000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>67363000</v>
+      </c>
+      <c r="E9" s="3">
         <v>64026000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>59000000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>57597000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>57947000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>56717000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>51445000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>46392000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>43589000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>41875000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>35764000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>35196000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>40775000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>42938000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>119519000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7685000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7017000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8571000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8387000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9097000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8681000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8367000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7370000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6371000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5415000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4772000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4750000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4583000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4244000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-73020000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,25 +900,26 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1600000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1500000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1700000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1500000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1300000</v>
       </c>
       <c r="I12" s="3">
         <v>1300000</v>
@@ -915,10 +928,10 @@
         <v>1300000</v>
       </c>
       <c r="K12" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="L12" s="3">
         <v>1200000</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,87 +999,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E14" s="3">
         <v>65000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>156000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>214000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-229000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>155000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-85000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>206000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-134000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>80000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>82000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>119000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>396000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>48000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>136000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1294000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1213000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1167000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1151000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1189000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1124000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1078000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1055000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1072000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1079,9 +1101,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>68057000</v>
+      </c>
+      <c r="E17" s="3">
         <v>63862000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>58513000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>58515000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>59223000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>56521000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>52114000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>47118000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>44367000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>41402000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>35824000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>34934000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>40853000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>42748000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>42479000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6991000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7181000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9058000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7469000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7821000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8877000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7698000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6644000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5593000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5888000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4712000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5012000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4505000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4434000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4020000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,248 +1245,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-140000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-112000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-48000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-69000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-104000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-111000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-68000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-170000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-471000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>30000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5000</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>21000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-35000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8345000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8534000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10337000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8668000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9079000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10105000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8887000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7767000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6835000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6632000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5768000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6011000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5495000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5443000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4993000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1118000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1036000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>916000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>623000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>569000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>591000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>653000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>668000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>651000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>663000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>443000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>340000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>350000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>383000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>354000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5922000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6220000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8098000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6680000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7550000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8235000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7241000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5838000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5246000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4754000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4299000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4677000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4155000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4072000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3631000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>905000</v>
+      </c>
+      <c r="E24" s="3">
         <v>884000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1178000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>948000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1235000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1347000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1011000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>792000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3356000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1093000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1173000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1424000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1205000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1327000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>964000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5017000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5336000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6920000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5732000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6315000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6888000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6230000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5046000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1890000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3661000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3126000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3253000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2950000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2745000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2667000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5017000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5336000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6920000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5732000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6315000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6833000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6230000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5046000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1963000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3661000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3126000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3253000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2950000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2745000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2655000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1663,38 +1723,41 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-55000</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>73000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>1512000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>479000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>361000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>31000</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-12000</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E32" s="3">
         <v>140000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>112000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>48000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>69000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>104000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>111000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>68000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>170000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>471000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-30000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5000</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>35000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5017000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5336000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6920000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5732000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6315000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6833000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6230000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5046000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1963000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5173000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3605000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3614000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2981000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2745000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2643000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5017000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5336000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6920000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5732000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6315000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6833000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6230000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5046000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1963000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5173000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3605000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3614000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2981000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2745000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2643000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,56 +2159,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4121000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2483000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1442000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2547000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3604000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3160000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1514000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>772000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2861000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1837000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1090000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1446000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2617000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1898000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3582000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2167,347 +2256,371 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>3000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16902000</v>
+      </c>
+      <c r="E43" s="3">
         <v>15308000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15315000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14823000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12542000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11523000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11431000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11916000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10257000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8202000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7254000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5877000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5834000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6563000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6064000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3524000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3474000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3132000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3088000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2981000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3545000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3619000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2997000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2878000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4670000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4819000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2804000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2977000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2937000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4962000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>815000</v>
+      </c>
+      <c r="E45" s="3">
         <v>584000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>632000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>533000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>688000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1150000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>531000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>418000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1509000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>399000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2873000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2195000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1901000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2457000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1967000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25362000</v>
+      </c>
+      <c r="E46" s="3">
         <v>21849000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20521000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20991000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19815000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19378000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17095000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16103000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17505000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15108000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14573000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12322000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13329000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13855000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14094000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>653000</v>
+      </c>
+      <c r="E47" s="3">
         <v>654000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>701000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>685000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>689000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>784000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>1200000</v>
       </c>
       <c r="J47" s="3">
         <v>1200000</v>
       </c>
       <c r="K47" s="3">
-        <v>1400000</v>
+        <v>1200000</v>
       </c>
       <c r="L47" s="3">
         <v>1400000</v>
       </c>
       <c r="M47" s="3">
+        <v>1400000</v>
+      </c>
+      <c r="N47" s="3">
         <v>1300000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>971000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>914000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>749000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1394000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9726000</v>
+        <v>9851000</v>
       </c>
       <c r="E48" s="3">
+        <v>8726000</v>
+      </c>
+      <c r="F48" s="3">
         <v>8370000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7975000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7597000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7213000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6591000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6124000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5775000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5549000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10879000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4751000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4706000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4675000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9222000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>14982000</v>
+        <v>15618000</v>
       </c>
       <c r="E49" s="3">
+        <v>14948000</v>
+      </c>
+      <c r="F49" s="3">
         <v>14411000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14158000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14296000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14504000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14328000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14710000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15028000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14857000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18864000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11186000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10348000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10370000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11012000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4849000</v>
+        <v>5381000</v>
       </c>
       <c r="E52" s="3">
+        <v>5883000</v>
+      </c>
+      <c r="F52" s="3">
         <v>5500000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5327000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6186000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5356000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4995000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3531000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3756000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10892000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18572000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7816000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6891000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9008000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11464000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>59840000</v>
+      </c>
+      <c r="E54" s="3">
         <v>55617000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>52456000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>52880000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>50873000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>50710000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>47528000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44876000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>46620000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>47806000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>49304000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>37046000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36188000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>38657000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37908000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,296 +2915,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3630000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2222000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2312000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2117000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>780000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>880000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1281000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2402000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1467000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1653000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1745000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1562000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1397000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2038000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2269000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>958000</v>
+        <v>1414000</v>
       </c>
       <c r="E58" s="3">
+        <v>643000</v>
+      </c>
+      <c r="F58" s="3">
         <v>168000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>118000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>500000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1250000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1500000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>750000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>956000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>150000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13115000</v>
+        <v>15107000</v>
       </c>
       <c r="E59" s="3">
+        <v>13430000</v>
+      </c>
+      <c r="F59" s="3">
         <v>11324000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10577000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10109000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9390000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8975000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8374000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8911000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10889000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11217000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9550000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9723000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9967000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9861000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23335000</v>
+      </c>
+      <c r="E60" s="3">
         <v>19420000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16937000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15887000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13997000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13933000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13972000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14398000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12913000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12542000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13918000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11112000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11120000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12155000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12130000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>20460000</v>
+        <v>21357000</v>
       </c>
       <c r="E61" s="3">
+        <v>19627000</v>
+      </c>
+      <c r="F61" s="3">
         <v>17291000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15429000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11670000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11669000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11404000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12604000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13513000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14282000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14305000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6142000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6152000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6158000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6460000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4613000</v>
+        <v>4512000</v>
       </c>
       <c r="E62" s="3">
+        <v>5446000</v>
+      </c>
+      <c r="F62" s="3">
         <v>5231000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6826000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5928000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6196000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5747000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4311000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4548000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19376000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>17779000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16392000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13998000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20305000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18317000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53119000</v>
+      </c>
+      <c r="E66" s="3">
         <v>49284000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45621000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>43614000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39914000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>44672000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>44357000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43427000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>47396000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>46295000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>46207000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33646000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>31270000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38618000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>36907000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14034000</v>
+      </c>
+      <c r="E72" s="3">
         <v>14551000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15398000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16943000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21600000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>21636000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18401000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15434000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11405000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13324000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14238000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14956000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14200000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>13211000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11937000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6721000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6333000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6835000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9266000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10959000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6015000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3127000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1394000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-850000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1511000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3097000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3400000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4918000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>39000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1001000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5017000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5336000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6920000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5732000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6315000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6833000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6230000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5046000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1963000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5173000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3605000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3614000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2981000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2745000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2643000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1040000</v>
+      </c>
+      <c r="E83" s="3">
         <v>966000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>920000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>903000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>904000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>853000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>794000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>759000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>760000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1215000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1026000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>994000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>990000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>988000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1008000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8557000</v>
+      </c>
+      <c r="E89" s="3">
         <v>6972000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7920000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7802000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9221000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8183000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7311000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3138000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6476000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5189000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5101000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3866000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4546000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1561000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4253000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1649000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1685000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1691000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1670000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1522000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1766000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1484000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1278000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1177000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1063000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-939000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-845000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-836000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-942000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1160000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1977000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1792000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1694000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1789000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1161000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2010000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1241000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1075000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1147000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-985000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9734000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1723000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1121000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1177000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-788000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,56 +4687,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3131000</v>
+      </c>
+      <c r="E96" s="3">
         <v>3059000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3056000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3016000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2940000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2764000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2556000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2347000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2163000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2048000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1932000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1760000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1540000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1352000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1095000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,57 +4888,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4942000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4139000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7331000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7070000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7616000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4527000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5328000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4152000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4305000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3457000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4277000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3314000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2706000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2068000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2144000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4724,8 +4972,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4742,55 +4990,61 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1638000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1041000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1105000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1057000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>444000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1646000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>742000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2089000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1024000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>747000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-356000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1171000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>719000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1684000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1321000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
